--- a/datosNivelesSin0PValues.xlsx
+++ b/datosNivelesSin0PValues.xlsx
@@ -528,10 +528,10 @@
         <v>0.4027220266890382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6915889473720215</v>
+        <v>0.675686199715456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5158819594644314</v>
+        <v>0.7616668145108536</v>
       </c>
       <c r="F2" t="n">
         <v>0.09608228180083961</v>
@@ -586,10 +586,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01668827158669292</v>
+        <v>0.01483860220629784</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02777104641199885</v>
+        <v>0.04089423170937587</v>
       </c>
       <c r="F3" t="n">
         <v>0.8251917970321139</v>
@@ -638,55 +638,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6915889473720215</v>
+        <v>0.675686199715456</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01668827158669292</v>
+        <v>0.01483860220629784</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00293687749033416</v>
+        <v>3.326134579727315e-39</v>
       </c>
       <c r="F4" t="n">
-        <v>6.175842046432139e-27</v>
+        <v>9.788403999935593e-27</v>
       </c>
       <c r="G4" t="n">
-        <v>4.108113373059605e-24</v>
+        <v>6.087405694230785e-24</v>
       </c>
       <c r="H4" t="n">
-        <v>2.360771682976241e-15</v>
+        <v>2.911871776705057e-15</v>
       </c>
       <c r="I4" t="n">
-        <v>1.087571322423177e-35</v>
+        <v>3.350671584672227e-35</v>
       </c>
       <c r="J4" t="n">
-        <v>2.283724637630625e-33</v>
+        <v>7.314257099471033e-33</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001233481817666085</v>
+        <v>0.001164499690233746</v>
       </c>
       <c r="L4" t="n">
-        <v>1.133318042664877e-15</v>
+        <v>1.2446332698973e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>9.206326610620993e-11</v>
+        <v>8.917780967694703e-11</v>
       </c>
       <c r="N4" t="n">
-        <v>4.794889582979034e-14</v>
+        <v>6.29316996881272e-14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.929239680576164e-67</v>
+        <v>4.228628731265958e-66</v>
       </c>
       <c r="P4" t="n">
-        <v>5.223439209245607e-45</v>
+        <v>1.837599722617359e-44</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002402668405465075</v>
+        <v>0.0002214323877117461</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002618090762698358</v>
+        <v>0.0002416866273269361</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +696,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5158819594644314</v>
+        <v>0.7616668145108536</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02777104641199885</v>
+        <v>0.04089423170937587</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00293687749033416</v>
+        <v>3.326134579727315e-39</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05947272217348997</v>
+        <v>1.021757253202189e-24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05543443064939885</v>
+        <v>5.080655163681751e-24</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2294027097068987</v>
+        <v>1.832680438632996e-11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2163483637745261</v>
+        <v>2.074994772352931e-27</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2920358012773351</v>
+        <v>1.455028432292174e-27</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2729169410582585</v>
+        <v>0.05132971239392058</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03591974299393782</v>
+        <v>2.120212672119236e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0184667871092466</v>
+        <v>7.413965673634087e-13</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3412645702117776</v>
+        <v>1.291805560334155e-11</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04172033844401593</v>
+        <v>1.562977340557566e-41</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07357450194133466</v>
+        <v>4.2070150420687e-34</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02353438476153773</v>
+        <v>4.134784737232227e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0381106527183314</v>
+        <v>3.555545036836807e-05</v>
       </c>
     </row>
     <row r="6">
@@ -760,10 +760,10 @@
         <v>0.8251917970321139</v>
       </c>
       <c r="D6" t="n">
-        <v>6.175842046432139e-27</v>
+        <v>9.788403999935593e-27</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05947272217348997</v>
+        <v>1.021757253202189e-24</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>0.9549792855341317</v>
       </c>
       <c r="D7" t="n">
-        <v>4.108113373059605e-24</v>
+        <v>6.087405694230785e-24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05543443064939885</v>
+        <v>5.080655163681751e-24</v>
       </c>
       <c r="F7" t="n">
         <v>1.585473666651916e-103</v>
@@ -876,10 +876,10 @@
         <v>0.5522205254653341</v>
       </c>
       <c r="D8" t="n">
-        <v>2.360771682976241e-15</v>
+        <v>2.911871776705057e-15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2294027097068987</v>
+        <v>1.832680438632996e-11</v>
       </c>
       <c r="F8" t="n">
         <v>8.669518014125323e-33</v>
@@ -934,10 +934,10 @@
         <v>0.4110260348949608</v>
       </c>
       <c r="D9" t="n">
-        <v>1.087571322423177e-35</v>
+        <v>3.350671584672227e-35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2163483637745261</v>
+        <v>2.074994772352931e-27</v>
       </c>
       <c r="F9" t="n">
         <v>3.553020648548806e-58</v>
@@ -992,10 +992,10 @@
         <v>0.5805839822868791</v>
       </c>
       <c r="D10" t="n">
-        <v>2.283724637630625e-33</v>
+        <v>7.314257099471033e-33</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2920358012773351</v>
+        <v>1.455028432292174e-27</v>
       </c>
       <c r="F10" t="n">
         <v>7.139171240823132e-56</v>
@@ -1050,10 +1050,10 @@
         <v>0.1604658291509544</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001233481817666085</v>
+        <v>0.001164499690233746</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2729169410582585</v>
+        <v>0.05132971239392058</v>
       </c>
       <c r="F11" t="n">
         <v>0.002657712779130271</v>
@@ -1108,10 +1108,10 @@
         <v>0.818548998513021</v>
       </c>
       <c r="D12" t="n">
-        <v>1.133318042664877e-15</v>
+        <v>1.2446332698973e-15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03591974299393782</v>
+        <v>2.120212672119236e-16</v>
       </c>
       <c r="F12" t="n">
         <v>2.431418845167577e-83</v>
@@ -1166,10 +1166,10 @@
         <v>0.6786517410866332</v>
       </c>
       <c r="D13" t="n">
-        <v>9.206326610620993e-11</v>
+        <v>8.917780967694703e-11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0184667871092466</v>
+        <v>7.413965673634087e-13</v>
       </c>
       <c r="F13" t="n">
         <v>7.805677316525705e-52</v>
@@ -1224,10 +1224,10 @@
         <v>0.8673553842769502</v>
       </c>
       <c r="D14" t="n">
-        <v>4.794889582979034e-14</v>
+        <v>6.29316996881272e-14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3412645702117776</v>
+        <v>1.291805560334155e-11</v>
       </c>
       <c r="F14" t="n">
         <v>1.323481762928769e-33</v>
@@ -1282,10 +1282,10 @@
         <v>0.4703503791299752</v>
       </c>
       <c r="D15" t="n">
-        <v>3.929239680576164e-67</v>
+        <v>4.228628731265958e-66</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04172033844401593</v>
+        <v>1.562977340557566e-41</v>
       </c>
       <c r="F15" t="n">
         <v>5.856841608244954e-36</v>
@@ -1340,10 +1340,10 @@
         <v>0.6094799341768797</v>
       </c>
       <c r="D16" t="n">
-        <v>5.223439209245607e-45</v>
+        <v>1.837599722617359e-44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07357450194133466</v>
+        <v>4.2070150420687e-34</v>
       </c>
       <c r="F16" t="n">
         <v>2.507032093712892e-37</v>
@@ -1398,10 +1398,10 @@
         <v>0.8591033364237106</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002402668405465075</v>
+        <v>0.0002214323877117461</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02353438476153773</v>
+        <v>4.134784737232227e-06</v>
       </c>
       <c r="F17" t="n">
         <v>0.2728014491272575</v>
@@ -1456,10 +1456,10 @@
         <v>0.5171869598385114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0002618090762698358</v>
+        <v>0.0002416866273269361</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0381106527183314</v>
+        <v>3.555545036836807e-05</v>
       </c>
       <c r="F18" t="n">
         <v>0.1901971395870209</v>

--- a/datosNivelesSin0PValues.xlsx
+++ b/datosNivelesSin0PValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -572,6 +582,12 @@
       <c r="R2" t="n">
         <v>0.5470404159047818</v>
       </c>
+      <c r="S2" t="n">
+        <v>0.2414662197148964</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2414662197148947</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -630,6 +646,12 @@
       <c r="R3" t="n">
         <v>0.5171869598385114</v>
       </c>
+      <c r="S3" t="n">
+        <v>0.8614173965813771</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8614173965813783</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -688,6 +710,12 @@
       <c r="R4" t="n">
         <v>0.0002416866273269361</v>
       </c>
+      <c r="S4" t="n">
+        <v>0.006169177968839084</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.006169177968839283</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -746,6 +774,12 @@
       <c r="R5" t="n">
         <v>3.555545036836807e-05</v>
       </c>
+      <c r="S5" t="n">
+        <v>0.03585875664334229</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.03585875664334302</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -804,6 +838,12 @@
       <c r="R6" t="n">
         <v>0.1901971395870209</v>
       </c>
+      <c r="S6" t="n">
+        <v>0.008549114451689212</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.008549114451689557</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -862,6 +902,12 @@
       <c r="R7" t="n">
         <v>0.4430085628481293</v>
       </c>
+      <c r="S7" t="n">
+        <v>0.6539098353570576</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6539098353570645</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -920,6 +966,12 @@
       <c r="R8" t="n">
         <v>0.01783144107216338</v>
       </c>
+      <c r="S8" t="n">
+        <v>3.761145547764145e-17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.76114554776467e-17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -978,6 +1030,12 @@
       <c r="R9" t="n">
         <v>0.03454727696156103</v>
       </c>
+      <c r="S9" t="n">
+        <v>0.01446709069450555</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.01446709069450612</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1036,6 +1094,12 @@
       <c r="R10" t="n">
         <v>0.1959978429801278</v>
       </c>
+      <c r="S10" t="n">
+        <v>0.1886782720323328</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1886782720323364</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1094,6 +1158,12 @@
       <c r="R11" t="n">
         <v>2.200125709525247e-05</v>
       </c>
+      <c r="S11" t="n">
+        <v>4.427624224413964e-09</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.427624224414117e-09</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1152,6 +1222,12 @@
       <c r="R12" t="n">
         <v>0.5606792899407839</v>
       </c>
+      <c r="S12" t="n">
+        <v>0.01576732510832774</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.01576732510832827</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1210,6 +1286,12 @@
       <c r="R13" t="n">
         <v>0.8916650031601087</v>
       </c>
+      <c r="S13" t="n">
+        <v>0.6620716614232701</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6620716614232638</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1268,6 +1350,12 @@
       <c r="R14" t="n">
         <v>0.2460725173906352</v>
       </c>
+      <c r="S14" t="n">
+        <v>3.008683170736558e-12</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.008683170736795e-12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1326,6 +1414,12 @@
       <c r="R15" t="n">
         <v>4.678998912750497e-05</v>
       </c>
+      <c r="S15" t="n">
+        <v>0.01481808116793291</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01481808116793321</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1384,6 +1478,12 @@
       <c r="R16" t="n">
         <v>0.0366701669217053</v>
       </c>
+      <c r="S16" t="n">
+        <v>0.03125325706951242</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.03125325706951344</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1442,6 +1542,12 @@
       <c r="R17" t="n">
         <v>1.371199052263077e-83</v>
       </c>
+      <c r="S17" t="n">
+        <v>0.0578098162409028</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.05780981624090199</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1498,6 +1604,140 @@
         <v>1.371199052263077e-83</v>
       </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.001807645647315152</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.001807645647315152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.2414662197148964</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8614173965813771</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.006169177968839084</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.03585875664334229</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.008549114451689212</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6539098353570576</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.761145547764145e-17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01446709069450555</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1886782720323328</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.427624224413964e-09</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.01576732510832774</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6620716614232701</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.008683170736558e-12</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01481808116793291</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.03125325706951242</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0578098162409028</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.001807645647315152</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.2414662197148947</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8614173965813783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.006169177968839283</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.03585875664334302</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.008549114451689557</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6539098353570645</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.76114554776467e-17</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.01446709069450612</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1886782720323364</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.427624224414117e-09</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.01576732510832827</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6620716614232638</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.008683170736795e-12</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.01481808116793321</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.03125325706951344</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.05780981624090199</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.001807645647315152</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
     </row>
